--- a/reports/thesis/research_design_proposal.xlsx
+++ b/reports/thesis/research_design_proposal.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Without re-ID: 0 TP for all 4 VLM models. With re-ID: best model achieves 24 TP.</t>
+          <t>Without re-ID: 18–21 TP across 4 VLM models (loitering, escape, handoff largely missed). With re-ID: best model (Gemini 3.6 Flash) achieves 25/30 TP (F1=0.847), recovering loitering 5/5, escape 1/5, handoff 5/5.</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Qwen2-Audio achieves perfect precision (1.000) and best F1=0.750; PANNs best F1=0.429. Optimal config: 2.5s window, 1.25s hop.</t>
+          <t>Qwen2-Audio achieves perfect precision (1.000) and best F1=0.788 at 5.0s/2.5s (F1=0.750 at 2.5s/1.25s); PANNs best F1=0.429 at 2.5s/1.25s. Optimal config: 5.0s window, 2.5s hop.</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>C achieves F1=0.875 with best combo (Gemini 3.6 Flash + Qwen2). C ≥ max(A, B) holds on all 30 scenes.</t>
+          <t>C achieves F1=0.938 with best combo (Gemini 3.6 Flash + Qwen2-Audio, 30/30 TP, 4 FP, 0 FN). Visual-only best: Gemini 3.6 Flash F1=0.847 (25/30 TP). C ≥ max(A, B) holds on all 30 scenes.</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>RQ1 (Re-ID): All 4 VLM models produce 0 TP without re-ID. RQ2 (Audio): Qwen2-Audio best F1=0.750 (P=1.000) at 2.5s/1.25s; PANNs best F1=0.429. RQ3 (Multimodal): Gemini 3.6 Flash + Qwen2-Audio = F1=0.875 (28/30 TP, 6 FP, 2 FN). Best visual alone: Gemini 3.6 Flash F1=0.800 (24/30 TP). Claim C ≥ max(A, B) holds on all 30 scenes.</t>
+          <t>RQ1 (Re-ID): Without re-ID, models produce 18–21 TP (loitering, escape, handoff mostly missed). With re-ID, best model Gemini 3.6 Flash achieves 25/30 TP (F1=0.847). RQ2 (Audio): Qwen2-Audio best F1=0.788 (P=1.000) at 5.0s/2.5s; PANNs best F1=0.429. RQ3 (Multimodal): Gemini 3.6 Flash + Qwen2-Audio = F1=0.938 (30/30 TP, 4 FP, 0 FN). Best visual alone: Gemini 3.6 Flash F1=0.847 (25/30 TP). Claim C ≥ max(A, B) holds on all 30 scenes.</t>
         </is>
       </c>
     </row>
